--- a/replication-package/replication/replication tracker.xlsx
+++ b/replication-package/replication/replication tracker.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10419"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\al2705\Princeton Dropbox\Allan Lee\TransferIncidence\replication\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/esoltas/Princeton Dropbox/Evan Soltas/Research/Completed/TransferIncidence/replication/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C7DA890-E297-4FA3-BCD3-771D85B141E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2CAA9A3-0133-904D-9B08-4652F28A0B3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-16245" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="980" yWindow="760" windowWidth="30240" windowHeight="17480" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="675" uniqueCount="372">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="675" uniqueCount="374">
   <si>
     <t>Number</t>
   </si>
@@ -67,9 +67,6 @@
     <t>eligregs_appear_2_eq_no.pdf</t>
   </si>
   <si>
-    <t>eligregs_between_within_lifetime.pdf</t>
-  </si>
-  <si>
     <t>participation_reg_mu.pdf</t>
   </si>
   <si>
@@ -373,9 +370,6 @@
     <t>A32</t>
   </si>
   <si>
-    <t>adversarial.pdf</t>
-  </si>
-  <si>
     <t>A2</t>
   </si>
   <si>
@@ -1099,9 +1093,6 @@
     <t>snap_by_month_final.tex</t>
   </si>
   <si>
-    <t>other_outcomes_c.tex</t>
-  </si>
-  <si>
     <t>table_A2</t>
   </si>
   <si>
@@ -1157,6 +1148,21 @@
   </si>
   <si>
     <t>Not applicable. Data compiled by hand by authors using publicly available sources.</t>
+  </si>
+  <si>
+    <t>other_outcomes.tex</t>
+  </si>
+  <si>
+    <t>adversarial_reg.pdf</t>
+  </si>
+  <si>
+    <t>rk_lifetime_eq_pred_income.pdf</t>
+  </si>
+  <si>
+    <t>eligregs_between_within_lifetime_yes.pdf</t>
+  </si>
+  <si>
+    <t>eligregs_between_within_lifetime_no.pdf</t>
   </si>
 </sst>
 </file>
@@ -1280,6 +1286,145 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="25">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="10"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF002060"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -1627,145 +1772,6 @@
         <scheme val="none"/>
       </font>
     </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="10"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF002060"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1780,48 +1786,48 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A3:F23" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A3:F23" totalsRowShown="0" headerRowDxfId="24" dataDxfId="23">
   <autoFilter ref="A3:F23" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Number" dataDxfId="14"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Export Name" dataDxfId="13"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Line Number" dataDxfId="12"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Title" dataDxfId="11"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="New File Name" dataDxfId="10"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Note" dataDxfId="9"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Number" dataDxfId="22"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Export Name" dataDxfId="21"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Line Number" dataDxfId="20"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Title" dataDxfId="19"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="New File Name" dataDxfId="18"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Note" dataDxfId="17"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table2" displayName="Table2" ref="A3:G58" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table2" displayName="Table2" ref="A3:G58" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
   <autoFilter ref="A3:G58" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Number" dataDxfId="6"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Export Name" dataDxfId="5"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="Line Number" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Title" dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Subtitle" dataDxfId="2"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="File Name" dataDxfId="1"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Note" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Number" dataDxfId="14"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Export Name" dataDxfId="13"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="Line Number" dataDxfId="12"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Title" dataDxfId="11"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Subtitle" dataDxfId="10"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="File Name" dataDxfId="9"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Note" dataDxfId="8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Table3" displayName="Table3" ref="A3:F66" totalsRowShown="0" headerRowDxfId="24" dataDxfId="23">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Table3" displayName="Table3" ref="A3:F66" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6">
   <autoFilter ref="A3:F66" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Data Name" dataDxfId="22"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Location" dataDxfId="21"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Link" dataDxfId="20">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Data Name" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Location" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Link" dataDxfId="3">
       <calculatedColumnFormula>IF(ISNA(D4)=TRUE,"",HYPERLINK(D4,"LINK"))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="URL" dataDxfId="19" dataCellStyle="Hyperlink"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Citation" dataDxfId="18"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Note" dataDxfId="17"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="URL" dataDxfId="2" dataCellStyle="Hyperlink"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Citation" dataDxfId="1"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Note" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2091,7 +2097,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F23"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="8.6640625" style="2" customWidth="1"/>
     <col min="2" max="2" width="28.33203125" style="2" customWidth="1"/>
@@ -2099,40 +2105,40 @@
     <col min="4" max="4" width="74.6640625" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="19.6640625" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="28.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="8.796875" style="2"/>
+    <col min="7" max="16384" width="8.83203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="22.5" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:6" ht="23" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
       <c r="D1" s="10"/>
       <c r="E1" s="10"/>
     </row>
-    <row r="2" spans="1:6" ht="3" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="1:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:6" ht="3" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A3" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="D3" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="E3" s="4" t="s">
-        <v>130</v>
-      </c>
       <c r="F3" s="4" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A4" s="7">
         <v>1</v>
       </c>
@@ -2143,361 +2149,361 @@
         <v>146</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A5" s="7">
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="C5" s="12">
         <v>129</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A6" s="7">
         <v>3</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>360</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A7" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="12" t="s">
-        <v>363</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A7" s="7" t="s">
-        <v>12</v>
-      </c>
       <c r="B7" s="2" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="C7" s="12">
         <v>129</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A8" s="7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="C8" s="12">
         <v>109</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A9" s="7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C9" s="12">
         <v>142</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A10" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>352</v>
+        <v>369</v>
       </c>
       <c r="C10" s="12">
         <v>163</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A11" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C11" s="12">
         <v>108</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A12" s="7" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C12" s="12">
         <v>557</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A13" s="7" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="C13" s="12">
         <v>100</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A14" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="C14" s="12">
         <v>100</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A15" s="7" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C15" s="12">
         <v>74</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A16" s="7" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C16" s="12">
         <v>109</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A17" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C17" s="12">
         <v>95</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A18" s="7" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C18" s="12">
         <v>101</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A19" s="7" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C19" s="12">
         <v>87</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A20" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C20" s="12">
         <v>64</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A21" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C21" s="12" t="e">
         <f>NA()</f>
         <v>#N/A</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E21" s="2" t="e">
         <f>NA()</f>
         <v>#N/A</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A22" s="7" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C22" s="12" t="e">
         <f>NA()</f>
         <v>#N/A</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="E22" s="2" t="e">
         <f>NA()</f>
         <v>#N/A</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A23" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C23" s="12">
         <v>38</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
   </sheetData>
@@ -2512,20 +2518,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G112"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.46484375" customWidth="1"/>
-    <col min="2" max="2" width="31.796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.46484375" customWidth="1"/>
+    <col min="1" max="1" width="9.5" customWidth="1"/>
+    <col min="2" max="2" width="31.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.5" customWidth="1"/>
     <col min="4" max="4" width="92" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="47.796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="47.83203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.46484375" customWidth="1"/>
+    <col min="7" max="7" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="22.5" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:7" ht="23" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -2533,31 +2539,31 @@
       <c r="E1" s="11"/>
       <c r="F1" s="11"/>
     </row>
-    <row r="2" spans="1:7" ht="3" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:7" ht="3" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="7" t="s">
         <v>3</v>
       </c>
@@ -2568,19 +2574,19 @@
         <v>649</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="7" t="s">
         <v>4</v>
       </c>
@@ -2591,1323 +2597,1323 @@
         <v>591</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="7" t="s">
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>8</v>
+        <v>373</v>
       </c>
       <c r="C6" s="12">
         <v>213</v>
       </c>
       <c r="D6" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>131</v>
-      </c>
       <c r="G6" s="2"/>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="7" t="s">
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C7" s="12">
         <v>206</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="G7" s="2"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="7">
         <v>2</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C8" s="12">
         <v>210</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E8" s="2" t="e">
         <f>NA()</f>
         <v>#N/A</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>12</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>13</v>
       </c>
       <c r="C9" s="12">
         <v>136</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E9" s="2" t="e">
         <f>NA()</f>
         <v>#N/A</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="G9" s="2"/>
     </row>
-    <row r="10" spans="1:7" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:7" ht="29" x14ac:dyDescent="0.2">
       <c r="A10" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>14</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>15</v>
       </c>
       <c r="C10" s="12">
         <v>256</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="G10" s="2"/>
     </row>
-    <row r="11" spans="1:7" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:7" ht="29" x14ac:dyDescent="0.2">
       <c r="A11" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>17</v>
       </c>
       <c r="C11" s="12">
         <v>256</v>
       </c>
       <c r="D11" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="E11" s="2" t="s">
-        <v>144</v>
-      </c>
       <c r="F11" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="G11" s="2"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>18</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>19</v>
       </c>
       <c r="C12" s="12">
         <v>98</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E12" s="2" t="e">
         <f>NA()</f>
         <v>#N/A</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G12" s="2"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>21</v>
       </c>
       <c r="C13" s="12">
         <v>141</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E13" s="2" t="e">
         <f>NA()</f>
         <v>#N/A</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G13" s="2"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>22</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>23</v>
       </c>
       <c r="C14" s="12">
         <v>181</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E14" s="2" t="e">
         <f>NA()</f>
         <v>#N/A</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="G14" s="2"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>24</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>25</v>
       </c>
       <c r="C15" s="12">
         <v>299</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G15" s="2"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>26</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>27</v>
       </c>
       <c r="C16" s="12">
         <v>283</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.45">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>29</v>
       </c>
       <c r="C17" s="12">
         <v>226</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="G17" s="2"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>30</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>31</v>
       </c>
       <c r="C18" s="12">
         <v>226</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E18" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="F18" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="F18" s="2" t="s">
-        <v>155</v>
-      </c>
       <c r="G18" s="2"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>32</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>33</v>
       </c>
       <c r="C19" s="12">
         <v>231</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E19" s="2" t="e">
         <f>NA()</f>
         <v>#N/A</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.45">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>35</v>
       </c>
       <c r="C20" s="12">
         <v>221</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G20" s="2"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>36</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>37</v>
       </c>
       <c r="C21" s="12">
         <v>221</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G21" s="2"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C22" s="12">
         <v>189</v>
       </c>
       <c r="D22" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="F22" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="E22" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>162</v>
-      </c>
       <c r="G22" s="2"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C23" s="12">
         <v>189</v>
       </c>
       <c r="D23" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="F23" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="E23" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>162</v>
-      </c>
       <c r="G23" s="2"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>44</v>
       </c>
       <c r="C24" s="12">
         <v>200</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="G24" s="2"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B25" s="2" t="s">
         <v>45</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>46</v>
       </c>
       <c r="C25" s="12">
         <v>199</v>
       </c>
       <c r="D25" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="E25" s="2" t="s">
-        <v>166</v>
-      </c>
       <c r="F25" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="G25" s="2"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B26" s="2" t="s">
         <v>47</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>48</v>
       </c>
       <c r="C26" s="12">
         <v>204</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E26" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="F26" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="F26" s="2" t="s">
-        <v>170</v>
-      </c>
       <c r="G26" s="2" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.45">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B27" s="2" t="s">
         <v>49</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>50</v>
       </c>
       <c r="C27" s="12">
         <v>204</v>
       </c>
       <c r="D27" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="E27" s="2" t="s">
-        <v>169</v>
-      </c>
       <c r="F27" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.45">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B28" s="2" t="s">
         <v>51</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>52</v>
       </c>
       <c r="C28" s="12">
         <v>169</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.45">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B29" s="2" t="s">
         <v>53</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>54</v>
       </c>
       <c r="C29" s="12">
         <v>169</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E29" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F29" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="F29" s="2" t="s">
-        <v>171</v>
-      </c>
       <c r="G29" s="2" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.45">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="B30" s="2" t="s">
         <v>55</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>56</v>
       </c>
       <c r="C30" s="12">
         <v>137</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E30" s="2" t="e">
         <f>NA()</f>
         <v>#N/A</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="G30" s="2"/>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B31" s="2" t="s">
         <v>57</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>58</v>
       </c>
       <c r="C31" s="12">
         <v>169</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E31" s="2" t="e">
         <f>NA()</f>
         <v>#N/A</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="G31" s="2"/>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B32" s="2" t="s">
         <v>59</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>60</v>
       </c>
       <c r="C32" s="12">
         <v>267</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="G32" s="2"/>
     </row>
-    <row r="33" spans="1:7" ht="16.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:7" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="B33" s="2" t="s">
         <v>61</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>62</v>
       </c>
       <c r="C33" s="12">
         <v>267</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="G33" s="2"/>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="B34" s="2" t="s">
         <v>63</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>64</v>
       </c>
       <c r="C34" s="12">
         <v>132</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E34" s="2" t="e">
         <f>NA()</f>
         <v>#N/A</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="G34" s="2"/>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="B35" s="2" t="s">
         <v>65</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>66</v>
       </c>
       <c r="C35" s="12">
         <v>126</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E35" s="2" t="e">
         <f>NA()</f>
         <v>#N/A</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="G35" s="2"/>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="B36" s="2" t="s">
         <v>67</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>68</v>
       </c>
       <c r="C36" s="12">
         <v>118</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E36" s="2" t="e">
         <f>NA()</f>
         <v>#N/A</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="G36" s="2"/>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="B37" s="2" t="s">
         <v>69</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>70</v>
       </c>
       <c r="C37" s="12">
         <v>156</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="E37" s="2" t="e">
         <f>NA()</f>
         <v>#N/A</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="G37" s="2"/>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C38" s="12">
         <v>255</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="G38" s="2"/>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="B39" s="2" t="s">
         <v>73</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>74</v>
       </c>
       <c r="C39" s="12">
         <v>255</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="G39" s="2"/>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="B40" s="2" t="s">
         <v>75</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>76</v>
       </c>
       <c r="C40" s="12">
         <v>187</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E40" s="2" t="e">
         <f>NA()</f>
         <v>#N/A</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="G40" s="2"/>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C41" s="12">
         <v>649</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G41" s="2"/>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C42" s="12">
         <v>591</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G42" s="2"/>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" s="7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>8</v>
+        <v>372</v>
       </c>
       <c r="C43" s="12">
         <v>213</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.45">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" s="7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C44" s="12">
         <v>291</v>
       </c>
       <c r="D44" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="E44" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="E44" s="2" t="s">
-        <v>192</v>
-      </c>
       <c r="F44" s="2" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="G44" s="2"/>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="B45" s="2" t="s">
         <v>84</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>85</v>
       </c>
       <c r="C45" s="12">
         <v>241</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="G45" s="2"/>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="B46" s="2" t="s">
         <v>86</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>87</v>
       </c>
       <c r="C46" s="12">
         <v>241</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="G46" s="2"/>
     </row>
-    <row r="47" spans="1:7" ht="16.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:7" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="B47" s="2" t="s">
         <v>88</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>89</v>
       </c>
       <c r="C47" s="12">
         <v>141</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E47" s="2" t="e">
         <f>NA()</f>
         <v>#N/A</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="G47" s="2"/>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="B48" s="2" t="s">
         <v>90</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>91</v>
       </c>
       <c r="C48" s="12">
         <v>183</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="G48" s="2"/>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="B49" s="2" t="s">
         <v>92</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>93</v>
       </c>
       <c r="C49" s="12">
         <v>183</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="G49" s="2"/>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C50" s="12">
         <v>220</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="G50" s="2"/>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C51" s="12">
         <v>220</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="G51" s="2"/>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C52" s="12">
         <v>525</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G52" s="2"/>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C53" s="12">
         <v>452</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G53" s="2"/>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A54" s="7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C54" s="12">
         <v>186</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="G54" s="2"/>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A55" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>104</v>
+        <v>371</v>
       </c>
       <c r="C55" s="12">
         <v>186</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="G55" s="2"/>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A56" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="B56" s="2" t="s">
         <v>105</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>106</v>
       </c>
       <c r="C56" s="12">
         <v>209</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E56" s="2" t="e">
         <f>NA()</f>
         <v>#N/A</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="G56" s="2"/>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A57" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="B57" s="2" t="s">
         <v>107</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>108</v>
       </c>
       <c r="C57" s="12">
         <v>131</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E57" s="2" t="e">
         <f>NA()</f>
         <v>#N/A</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.45">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A58" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>110</v>
+        <v>370</v>
       </c>
       <c r="C58" s="12">
         <v>126</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="G58" s="2"/>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
       <c r="G59" s="2"/>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
       <c r="G60" s="2"/>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
       <c r="G61" s="2"/>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
       <c r="G62" s="2"/>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
       <c r="G63" s="2"/>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
       <c r="G64" s="2"/>
     </row>
-    <row r="65" spans="7:7" x14ac:dyDescent="0.45">
+    <row r="65" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G65" s="2"/>
     </row>
-    <row r="66" spans="7:7" x14ac:dyDescent="0.45">
+    <row r="66" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G66" s="2"/>
     </row>
-    <row r="67" spans="7:7" x14ac:dyDescent="0.45">
+    <row r="67" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G67" s="2"/>
     </row>
-    <row r="68" spans="7:7" x14ac:dyDescent="0.45">
+    <row r="68" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G68" s="2"/>
     </row>
-    <row r="69" spans="7:7" x14ac:dyDescent="0.45">
+    <row r="69" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G69" s="2"/>
     </row>
-    <row r="70" spans="7:7" x14ac:dyDescent="0.45">
+    <row r="70" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G70" s="2"/>
     </row>
-    <row r="71" spans="7:7" x14ac:dyDescent="0.45">
+    <row r="71" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G71" s="2"/>
     </row>
-    <row r="72" spans="7:7" x14ac:dyDescent="0.45">
+    <row r="72" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G72" s="2"/>
     </row>
-    <row r="73" spans="7:7" x14ac:dyDescent="0.45">
+    <row r="73" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G73" s="2"/>
     </row>
-    <row r="74" spans="7:7" x14ac:dyDescent="0.45">
+    <row r="74" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G74" s="2"/>
     </row>
-    <row r="75" spans="7:7" x14ac:dyDescent="0.45">
+    <row r="75" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G75" s="2"/>
     </row>
-    <row r="76" spans="7:7" x14ac:dyDescent="0.45">
+    <row r="76" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G76" s="2"/>
     </row>
-    <row r="77" spans="7:7" x14ac:dyDescent="0.45">
+    <row r="77" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G77" s="2"/>
     </row>
-    <row r="78" spans="7:7" x14ac:dyDescent="0.45">
+    <row r="78" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G78" s="2"/>
     </row>
-    <row r="79" spans="7:7" x14ac:dyDescent="0.45">
+    <row r="79" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G79" s="2"/>
     </row>
-    <row r="80" spans="7:7" x14ac:dyDescent="0.45">
+    <row r="80" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G80" s="2"/>
     </row>
-    <row r="81" spans="7:7" x14ac:dyDescent="0.45">
+    <row r="81" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G81" s="2"/>
     </row>
-    <row r="82" spans="7:7" x14ac:dyDescent="0.45">
+    <row r="82" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G82" s="2"/>
     </row>
-    <row r="83" spans="7:7" x14ac:dyDescent="0.45">
+    <row r="83" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G83" s="2"/>
     </row>
-    <row r="84" spans="7:7" x14ac:dyDescent="0.45">
+    <row r="84" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G84" s="2"/>
     </row>
-    <row r="85" spans="7:7" x14ac:dyDescent="0.45">
+    <row r="85" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G85" s="2"/>
     </row>
-    <row r="86" spans="7:7" x14ac:dyDescent="0.45">
+    <row r="86" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G86" s="2"/>
     </row>
-    <row r="87" spans="7:7" x14ac:dyDescent="0.45">
+    <row r="87" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G87" s="2"/>
     </row>
-    <row r="88" spans="7:7" x14ac:dyDescent="0.45">
+    <row r="88" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G88" s="2"/>
     </row>
-    <row r="89" spans="7:7" x14ac:dyDescent="0.45">
+    <row r="89" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G89" s="2"/>
     </row>
-    <row r="90" spans="7:7" x14ac:dyDescent="0.45">
+    <row r="90" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G90" s="2"/>
     </row>
-    <row r="91" spans="7:7" x14ac:dyDescent="0.45">
+    <row r="91" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G91" s="2"/>
     </row>
-    <row r="92" spans="7:7" x14ac:dyDescent="0.45">
+    <row r="92" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G92" s="2"/>
     </row>
-    <row r="93" spans="7:7" x14ac:dyDescent="0.45">
+    <row r="93" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G93" s="2"/>
     </row>
-    <row r="94" spans="7:7" x14ac:dyDescent="0.45">
+    <row r="94" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G94" s="2"/>
     </row>
-    <row r="95" spans="7:7" x14ac:dyDescent="0.45">
+    <row r="95" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G95" s="2"/>
     </row>
-    <row r="96" spans="7:7" x14ac:dyDescent="0.45">
+    <row r="96" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G96" s="2"/>
     </row>
-    <row r="97" spans="7:7" x14ac:dyDescent="0.45">
+    <row r="97" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G97" s="2"/>
     </row>
-    <row r="98" spans="7:7" x14ac:dyDescent="0.45">
+    <row r="98" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G98" s="2"/>
     </row>
-    <row r="99" spans="7:7" x14ac:dyDescent="0.45">
+    <row r="99" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G99" s="2"/>
     </row>
-    <row r="100" spans="7:7" x14ac:dyDescent="0.45">
+    <row r="100" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G100" s="2"/>
     </row>
-    <row r="101" spans="7:7" x14ac:dyDescent="0.45">
+    <row r="101" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G101" s="2"/>
     </row>
-    <row r="102" spans="7:7" x14ac:dyDescent="0.45">
+    <row r="102" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G102" s="2"/>
     </row>
-    <row r="103" spans="7:7" x14ac:dyDescent="0.45">
+    <row r="103" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G103" s="2"/>
     </row>
-    <row r="104" spans="7:7" x14ac:dyDescent="0.45">
+    <row r="104" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G104" s="2"/>
     </row>
-    <row r="105" spans="7:7" x14ac:dyDescent="0.45">
+    <row r="105" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G105" s="2"/>
     </row>
-    <row r="106" spans="7:7" x14ac:dyDescent="0.45">
+    <row r="106" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G106" s="2"/>
     </row>
-    <row r="107" spans="7:7" x14ac:dyDescent="0.45">
+    <row r="107" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G107" s="2"/>
     </row>
-    <row r="108" spans="7:7" x14ac:dyDescent="0.45">
+    <row r="108" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G108" s="2"/>
     </row>
-    <row r="109" spans="7:7" x14ac:dyDescent="0.45">
+    <row r="109" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G109" s="2"/>
     </row>
-    <row r="110" spans="7:7" x14ac:dyDescent="0.45">
+    <row r="110" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G110" s="2"/>
     </row>
-    <row r="111" spans="7:7" x14ac:dyDescent="0.45">
+    <row r="111" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G111" s="2"/>
     </row>
-    <row r="112" spans="7:7" x14ac:dyDescent="0.45">
+    <row r="112" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G112" s="2"/>
     </row>
   </sheetData>
@@ -3922,19 +3928,19 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:F66"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="14.25" outlineLevelCol="1" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" outlineLevelCol="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="60.796875" customWidth="1"/>
+    <col min="1" max="1" width="60.83203125" customWidth="1"/>
     <col min="2" max="2" width="52" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.46484375" customWidth="1"/>
-    <col min="4" max="4" width="108.1328125" customWidth="1" outlineLevel="1"/>
+    <col min="3" max="3" width="6.5" customWidth="1"/>
+    <col min="4" max="4" width="108.1640625" customWidth="1" outlineLevel="1"/>
     <col min="5" max="5" width="151.33203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="66.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="23.25" x14ac:dyDescent="0.7">
+    <row r="1" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
@@ -3942,716 +3948,716 @@
       <c r="E1" s="9"/>
       <c r="F1" s="9"/>
     </row>
-    <row r="2" spans="1:6" ht="3" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:6" ht="3" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>310</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>311</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>336</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>304</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>312</v>
-      </c>
       <c r="F3" s="4" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C4" s="3" t="str">
         <f>IF(ISNA(D4)=TRUE,"",HYPERLINK(D4,"LINK"))</f>
         <v>LINK</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C5" s="3" t="str">
         <f t="shared" ref="C5:C66" si="0">IF(ISNA(D5)=TRUE,"",HYPERLINK(D5,"LINK"))</f>
         <v>LINK</v>
       </c>
       <c r="D5" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="C6" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>LINK</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="C7" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>LINK</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="C8" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>LINK</v>
+      </c>
+      <c r="D8" s="5" t="s">
         <v>305</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A6" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="C6" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>LINK</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>305</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A7" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="B7" s="1" t="s">
+      <c r="E8" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A9" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="C7" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>LINK</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>305</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A8" s="2" t="s">
+      <c r="C9" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>LINK</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="F9" s="2"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="C10" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>LINK</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="F10" s="2"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="C11" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>LINK</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="C8" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>LINK</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A9" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="C9" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>LINK</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>306</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="F9" s="2"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A10" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="C10" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>LINK</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>306</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="F10" s="2"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A11" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="C11" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>LINK</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>306</v>
-      </c>
-      <c r="E11" s="2" t="s">
+      <c r="F11" s="2"/>
+    </row>
+    <row r="12" spans="1:6" ht="29" x14ac:dyDescent="0.2">
+      <c r="A12" s="6" t="s">
         <v>317</v>
       </c>
-      <c r="F11" s="2"/>
-    </row>
-    <row r="12" spans="1:6" ht="26.25" x14ac:dyDescent="0.45">
-      <c r="A12" s="6" t="s">
-        <v>319</v>
-      </c>
       <c r="B12" s="2" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C12" s="3" t="str">
         <f t="shared" ref="C12" si="1">IF(ISNA(D12)=TRUE,"",HYPERLINK(D12,"LINK"))</f>
         <v>LINK</v>
       </c>
       <c r="D12" s="5" t="s">
+        <v>316</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>318</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="F12" s="2"/>
+    </row>
+    <row r="13" spans="1:6" ht="29" x14ac:dyDescent="0.2">
+      <c r="A13" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="C13" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>LINK</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>316</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="F13" s="2"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A14" s="6" t="s">
+        <v>319</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="C14" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>LINK</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="F14" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="F12" s="2"/>
-    </row>
-    <row r="13" spans="1:6" ht="26.25" x14ac:dyDescent="0.45">
-      <c r="A13" s="6" t="s">
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A15" s="6" t="s">
         <v>319</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="C13" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>LINK</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>318</v>
-      </c>
-      <c r="E13" s="2" t="s">
+      <c r="B15" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="C15" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>LINK</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="F15" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="F13" s="2"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A14" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="B14" s="1" t="s">
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A16" s="6" t="s">
+        <v>319</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="C14" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>LINK</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A15" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="B15" s="1" t="s">
+      <c r="C16" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>LINK</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A17" s="6" t="s">
+        <v>319</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="C15" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>LINK</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A16" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="B16" s="1" t="s">
+      <c r="C17" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>LINK</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A18" s="6" t="s">
+        <v>319</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="C16" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>LINK</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A17" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="B17" s="1" t="s">
+      <c r="C18" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>LINK</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A19" s="6" t="s">
+        <v>319</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="C17" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>LINK</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A18" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="B18" s="1" t="s">
+      <c r="C19" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>LINK</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A20" s="6" t="s">
+        <v>319</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="C18" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>LINK</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A19" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="B19" s="1" t="s">
+      <c r="C20" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>LINK</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A21" s="6" t="s">
+        <v>319</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="C19" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>LINK</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A20" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="B20" s="1" t="s">
+      <c r="C21" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>LINK</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A22" s="6" t="s">
+        <v>319</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="C20" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>LINK</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A21" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="B21" s="1" t="s">
+      <c r="C22" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>LINK</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A23" s="6" t="s">
+        <v>319</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="C21" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>LINK</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A22" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="B22" s="1" t="s">
+      <c r="C23" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>LINK</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A24" s="6" t="s">
+        <v>319</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="C22" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>LINK</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A23" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="B23" s="1" t="s">
+      <c r="C24" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>LINK</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A25" s="6" t="s">
+        <v>319</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="C23" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>LINK</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A24" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="B24" s="1" t="s">
+      <c r="C25" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>LINK</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A26" s="6" t="s">
+        <v>319</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="C24" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>LINK</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A25" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="B25" s="1" t="s">
+      <c r="C26" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>LINK</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A27" s="6" t="s">
+        <v>319</v>
+      </c>
+      <c r="B27" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="C25" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>LINK</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A26" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="B26" s="1" t="s">
+      <c r="C27" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>LINK</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A28" s="6" t="s">
+        <v>319</v>
+      </c>
+      <c r="B28" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="C26" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>LINK</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A27" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="B27" s="1" t="s">
+      <c r="C28" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>LINK</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A29" s="6" t="s">
+        <v>319</v>
+      </c>
+      <c r="B29" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="C27" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>LINK</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A28" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="B28" s="1" t="s">
+      <c r="C29" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>LINK</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A30" s="6" t="s">
+        <v>319</v>
+      </c>
+      <c r="B30" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="C28" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>LINK</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A29" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="B29" s="1" t="s">
+      <c r="C30" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>LINK</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A31" s="6" t="s">
+        <v>319</v>
+      </c>
+      <c r="B31" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="C29" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>LINK</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A30" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="B30" s="1" t="s">
+      <c r="C31" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>LINK</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A32" s="6" t="s">
+        <v>319</v>
+      </c>
+      <c r="B32" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="C30" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>LINK</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A31" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="B31" s="1" t="s">
+      <c r="C32" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>LINK</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A33" s="6" t="s">
+        <v>319</v>
+      </c>
+      <c r="B33" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="C31" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>LINK</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A32" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="B32" s="1" t="s">
+      <c r="C33" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>LINK</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A34" s="6" t="s">
+        <v>319</v>
+      </c>
+      <c r="B34" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="C32" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>LINK</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A33" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="B33" s="1" t="s">
+      <c r="C34" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>LINK</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A35" s="6" t="s">
+        <v>319</v>
+      </c>
+      <c r="B35" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="C33" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>LINK</v>
-      </c>
-      <c r="D33" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A34" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="B34" s="1" t="s">
+      <c r="C35" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>LINK</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A36" s="6" t="s">
+        <v>319</v>
+      </c>
+      <c r="B36" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="C34" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>LINK</v>
-      </c>
-      <c r="D34" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A35" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="B35" s="1" t="s">
+      <c r="C36" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>LINK</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A37" s="6" t="s">
+        <v>336</v>
+      </c>
+      <c r="B37" s="1" t="s">
         <v>269</v>
-      </c>
-      <c r="C35" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>LINK</v>
-      </c>
-      <c r="D35" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="F35" s="2" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A36" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="C36" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>LINK</v>
-      </c>
-      <c r="D36" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="F36" s="2" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A37" s="6" t="s">
-        <v>338</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>271</v>
       </c>
       <c r="C37" s="3" t="str">
         <f t="shared" si="0"/>
@@ -4662,18 +4668,18 @@
         <v>#N/A</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.45">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A38" s="6" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C38" s="3" t="str">
         <f t="shared" si="0"/>
@@ -4684,18 +4690,18 @@
         <v>#N/A</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.45">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A39" s="6" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C39" s="3" t="str">
         <f t="shared" si="0"/>
@@ -4706,18 +4712,18 @@
         <v>#N/A</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.45">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A40" s="6" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C40" s="3" t="str">
         <f t="shared" si="0"/>
@@ -4728,18 +4734,18 @@
         <v>#N/A</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.45">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A41" s="6" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C41" s="3" t="str">
         <f t="shared" si="0"/>
@@ -4750,18 +4756,18 @@
         <v>#N/A</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.45">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A42" s="6" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C42" s="3" t="str">
         <f t="shared" si="0"/>
@@ -4772,37 +4778,37 @@
         <v>#N/A</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.45">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A43" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="C43" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>LINK</v>
+      </c>
+      <c r="D43" s="5" t="s">
         <v>328</v>
       </c>
-      <c r="B43" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="C43" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>LINK</v>
-      </c>
-      <c r="D43" s="5" t="s">
-        <v>330</v>
-      </c>
       <c r="E43" s="2" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="F43" s="2"/>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A44" s="6" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C44" s="3" t="str">
         <f t="shared" si="0"/>
@@ -4813,18 +4819,18 @@
         <v>#N/A</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.45">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A45" s="6" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C45" s="3" t="str">
         <f t="shared" si="0"/>
@@ -4835,451 +4841,451 @@
         <v>#N/A</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.45">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A46" s="6" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B46" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="C46" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>LINK</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A47" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="C47" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>LINK</v>
+      </c>
+      <c r="D47" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A48" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="B48" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="C46" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>LINK</v>
-      </c>
-      <c r="D46" s="5" t="s">
-        <v>308</v>
-      </c>
-      <c r="E46" s="2" t="s">
+      <c r="C48" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>LINK</v>
+      </c>
+      <c r="D48" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="F48" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="F46" s="2" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A47" s="6" t="s">
-        <v>341</v>
-      </c>
-      <c r="B47" s="1" t="s">
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A49" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="B49" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="C47" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>LINK</v>
-      </c>
-      <c r="D47" s="5" t="s">
-        <v>308</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="F47" s="2" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A48" s="6" t="s">
-        <v>341</v>
-      </c>
-      <c r="B48" s="1" t="s">
+      <c r="C49" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>LINK</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A50" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="B50" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="C48" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>LINK</v>
-      </c>
-      <c r="D48" s="5" t="s">
-        <v>308</v>
-      </c>
-      <c r="E48" s="2" t="s">
+      <c r="C50" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>LINK</v>
+      </c>
+      <c r="D50" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="F50" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="F48" s="2" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A49" s="6" t="s">
-        <v>341</v>
-      </c>
-      <c r="B49" s="1" t="s">
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A51" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="B51" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="C49" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>LINK</v>
-      </c>
-      <c r="D49" s="5" t="s">
-        <v>308</v>
-      </c>
-      <c r="E49" s="2" t="s">
+      <c r="C51" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>LINK</v>
+      </c>
+      <c r="D51" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="F51" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="F49" s="2" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A50" s="6" t="s">
-        <v>341</v>
-      </c>
-      <c r="B50" s="1" t="s">
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A52" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="B52" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="C50" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>LINK</v>
-      </c>
-      <c r="D50" s="5" t="s">
-        <v>308</v>
-      </c>
-      <c r="E50" s="2" t="s">
+      <c r="C52" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>LINK</v>
+      </c>
+      <c r="D52" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="F52" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="F50" s="2" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A51" s="6" t="s">
-        <v>341</v>
-      </c>
-      <c r="B51" s="1" t="s">
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A53" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="B53" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="C51" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>LINK</v>
-      </c>
-      <c r="D51" s="5" t="s">
-        <v>308</v>
-      </c>
-      <c r="E51" s="2" t="s">
+      <c r="C53" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>LINK</v>
+      </c>
+      <c r="D53" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="F53" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="F51" s="2" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A52" s="6" t="s">
-        <v>341</v>
-      </c>
-      <c r="B52" s="1" t="s">
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A54" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="B54" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="C52" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>LINK</v>
-      </c>
-      <c r="D52" s="5" t="s">
-        <v>308</v>
-      </c>
-      <c r="E52" s="2" t="s">
+      <c r="C54" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>LINK</v>
+      </c>
+      <c r="D54" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="F54" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="F52" s="2" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A53" s="6" t="s">
-        <v>341</v>
-      </c>
-      <c r="B53" s="1" t="s">
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A55" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="B55" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="C53" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>LINK</v>
-      </c>
-      <c r="D53" s="5" t="s">
-        <v>308</v>
-      </c>
-      <c r="E53" s="2" t="s">
+      <c r="C55" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>LINK</v>
+      </c>
+      <c r="D55" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="F55" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="F53" s="2" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A54" s="6" t="s">
-        <v>341</v>
-      </c>
-      <c r="B54" s="1" t="s">
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A56" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="B56" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="C54" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>LINK</v>
-      </c>
-      <c r="D54" s="5" t="s">
-        <v>308</v>
-      </c>
-      <c r="E54" s="2" t="s">
+      <c r="C56" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>LINK</v>
+      </c>
+      <c r="D56" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="F56" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="F54" s="2" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A55" s="6" t="s">
-        <v>341</v>
-      </c>
-      <c r="B55" s="1" t="s">
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A57" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="B57" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="C55" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>LINK</v>
-      </c>
-      <c r="D55" s="5" t="s">
-        <v>308</v>
-      </c>
-      <c r="E55" s="2" t="s">
+      <c r="C57" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>LINK</v>
+      </c>
+      <c r="D57" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="F57" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="F55" s="2" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A56" s="6" t="s">
-        <v>341</v>
-      </c>
-      <c r="B56" s="1" t="s">
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A58" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="B58" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="C56" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>LINK</v>
-      </c>
-      <c r="D56" s="5" t="s">
-        <v>308</v>
-      </c>
-      <c r="E56" s="2" t="s">
+      <c r="C58" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>LINK</v>
+      </c>
+      <c r="D58" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="F58" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="F56" s="2" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A57" s="6" t="s">
-        <v>341</v>
-      </c>
-      <c r="B57" s="1" t="s">
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A59" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="B59" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="C57" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>LINK</v>
-      </c>
-      <c r="D57" s="5" t="s">
-        <v>308</v>
-      </c>
-      <c r="E57" s="2" t="s">
+      <c r="C59" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>LINK</v>
+      </c>
+      <c r="D59" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="F59" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="F57" s="2" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A58" s="6" t="s">
-        <v>341</v>
-      </c>
-      <c r="B58" s="1" t="s">
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A60" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="B60" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="C58" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>LINK</v>
-      </c>
-      <c r="D58" s="5" t="s">
-        <v>308</v>
-      </c>
-      <c r="E58" s="2" t="s">
+      <c r="C60" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>LINK</v>
+      </c>
+      <c r="D60" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="F60" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="F58" s="2" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A59" s="6" t="s">
-        <v>341</v>
-      </c>
-      <c r="B59" s="1" t="s">
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A61" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="B61" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="C59" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>LINK</v>
-      </c>
-      <c r="D59" s="5" t="s">
-        <v>308</v>
-      </c>
-      <c r="E59" s="2" t="s">
+      <c r="C61" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>LINK</v>
+      </c>
+      <c r="D61" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="F61" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="F59" s="2" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A60" s="6" t="s">
-        <v>341</v>
-      </c>
-      <c r="B60" s="1" t="s">
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A62" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="B62" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="C60" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>LINK</v>
-      </c>
-      <c r="D60" s="5" t="s">
-        <v>308</v>
-      </c>
-      <c r="E60" s="2" t="s">
+      <c r="C62" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>LINK</v>
+      </c>
+      <c r="D62" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="F62" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="F60" s="2" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A61" s="6" t="s">
-        <v>341</v>
-      </c>
-      <c r="B61" s="1" t="s">
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A63" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="B63" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="C61" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>LINK</v>
-      </c>
-      <c r="D61" s="5" t="s">
-        <v>308</v>
-      </c>
-      <c r="E61" s="2" t="s">
+      <c r="C63" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>LINK</v>
+      </c>
+      <c r="D63" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="F63" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="F61" s="2" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A62" s="6" t="s">
-        <v>341</v>
-      </c>
-      <c r="B62" s="1" t="s">
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A64" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="B64" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="C62" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>LINK</v>
-      </c>
-      <c r="D62" s="5" t="s">
-        <v>308</v>
-      </c>
-      <c r="E62" s="2" t="s">
+      <c r="C64" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>LINK</v>
+      </c>
+      <c r="D64" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="F64" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="F62" s="2" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A63" s="6" t="s">
-        <v>341</v>
-      </c>
-      <c r="B63" s="1" t="s">
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A65" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="B65" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="C63" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>LINK</v>
-      </c>
-      <c r="D63" s="5" t="s">
-        <v>308</v>
-      </c>
-      <c r="E63" s="2" t="s">
+      <c r="C65" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>LINK</v>
+      </c>
+      <c r="D65" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="F65" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="F63" s="2" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A64" s="6" t="s">
-        <v>341</v>
-      </c>
-      <c r="B64" s="1" t="s">
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A66" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="B66" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="C64" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>LINK</v>
-      </c>
-      <c r="D64" s="5" t="s">
-        <v>308</v>
-      </c>
-      <c r="E64" s="2" t="s">
+      <c r="C66" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>LINK</v>
+      </c>
+      <c r="D66" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="F66" s="2" t="s">
         <v>332</v>
-      </c>
-      <c r="F64" s="2" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A65" s="6" t="s">
-        <v>341</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="C65" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>LINK</v>
-      </c>
-      <c r="D65" s="5" t="s">
-        <v>308</v>
-      </c>
-      <c r="E65" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="F65" s="2" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A66" s="6" t="s">
-        <v>341</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="C66" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>LINK</v>
-      </c>
-      <c r="D66" s="5" t="s">
-        <v>308</v>
-      </c>
-      <c r="E66" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="F66" s="2" t="s">
-        <v>334</v>
       </c>
     </row>
   </sheetData>
